--- a/RCIX4N.xlsx
+++ b/RCIX4N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="85">
   <si>
     <t/>
   </si>
@@ -175,6 +175,15 @@
     <t>16</t>
   </si>
   <si>
+    <t>20144201</t>
+  </si>
+  <si>
+    <t>CMPN HULA ESDOGER 45</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>20140182</t>
   </si>
   <si>
@@ -209,12 +218,6 @@
   </si>
   <si>
     <t>CAMPINA HAPPY COW 85</t>
-  </si>
-  <si>
-    <t>20121363</t>
-  </si>
-  <si>
-    <t>CMPN MCH DUO VAN CHK</t>
   </si>
   <si>
     <t>20137105</t>
@@ -1017,10 +1020,10 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>26</v>
@@ -1028,10 +1031,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1040,7 +1043,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>26</v>
@@ -1048,10 +1051,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1060,7 +1063,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>26</v>
@@ -1068,10 +1071,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1080,18 +1083,18 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1100,7 +1103,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1108,10 +1111,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1120,7 +1123,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1128,10 +1131,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1140,18 +1143,18 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1168,10 +1171,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1188,10 +1191,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1208,10 +1211,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1228,10 +1231,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1248,10 +1251,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1268,10 +1271,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1288,10 +1291,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
